--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,123 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131172052</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101215</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rökärret/Blackstahyttan, Rökärret/Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>500129</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6581382</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Många fynd i det avverkningsanmälda området</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131172052</v>
       </c>
       <c r="B3" t="n">
-        <v>101215</v>
+        <v>101216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131172052</v>
       </c>
       <c r="B3" t="n">
-        <v>101216</v>
+        <v>101217</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131172052</v>
       </c>
       <c r="B3" t="n">
-        <v>101217</v>
+        <v>101220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131172052</v>
       </c>
       <c r="B3" t="n">
-        <v>101220</v>
+        <v>101221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131172052</v>
       </c>
       <c r="B3" t="n">
-        <v>101221</v>
+        <v>101223</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131172052</v>
       </c>
       <c r="B3" t="n">
-        <v>101223</v>
+        <v>101224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131172052</v>
       </c>
       <c r="B3" t="n">
-        <v>101224</v>
+        <v>101225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131172052</v>
       </c>
       <c r="B3" t="n">
-        <v>101225</v>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131172052</v>
       </c>
       <c r="B3" t="n">
-        <v>101228</v>
+        <v>101231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131172052</v>
       </c>
       <c r="B3" t="n">
-        <v>101231</v>
+        <v>101237</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58220495</v>
+        <v>130210272</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>937</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rökärret 3650/4350, Nrk</t>
+          <t>Klockhammar, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>500126.939481183</v>
+        <v>500179</v>
       </c>
       <c r="R2" t="n">
-        <v>6581371.413665434</v>
+        <v>6581423</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1986-05-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1986-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,65 +769,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131172052</v>
+        <v>129001124</v>
       </c>
       <c r="B3" t="n">
-        <v>101237</v>
+        <v>92732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2014</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rökärret/Blackstahyttan, Rökärret/Blackstahyttan, Nrk</t>
+          <t>Klockhammar, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>500129</v>
+        <v>500201</v>
       </c>
       <c r="R3" t="n">
-        <v>6581382</v>
+        <v>6581439</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,27 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Många fynd i det avverkningsanmälda området</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,15 +875,445 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130210277</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92732</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Klockhammar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>500201</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6581440</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>117766700</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klockhammar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500115</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6581489</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>58220495</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rökärret 3650/4350, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500127</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6581371</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1986-05-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1986-05-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131172052</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rökärret/Blackstahyttan, Rökärret/Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500129</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6581382</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många fynd i det avverkningsanmälda området</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Lotta Sörman</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Lotta Sörman</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63196-2025 artfynd.xlsx
+++ b/artfynd/A 63196-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210272</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001124</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130210277</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766700</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58220495</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,8 +1344,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131172052</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>